--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="93">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -292,6 +292,12 @@
   </si>
   <si>
     <t>Practice Status</t>
+  </si>
+  <si>
+    <t>Duplicate Check</t>
+  </si>
+  <si>
+    <t>Data Quality Validation</t>
   </si>
 </sst>
 </file>
@@ -631,14 +637,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="1" max="2" width="22.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2290,6 +2295,57 @@
         <v>0</v>
       </c>
     </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C98" t="s">
+        <v>92</v>
+      </c>
+      <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99" t="s">
+        <v>92</v>
+      </c>
+      <c r="D99" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>13</v>
+      </c>
+      <c r="B100" t="s">
+        <v>91</v>
+      </c>
+      <c r="C100" t="s">
+        <v>92</v>
+      </c>
+      <c r="D100" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="94">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -297,7 +297,10 @@
     <t>Duplicate Check</t>
   </si>
   <si>
-    <t>Data Quality Validation</t>
+    <t>Practicecode</t>
+  </si>
+  <si>
+    <t>Null Check</t>
   </si>
 </sst>
 </file>
@@ -637,13 +640,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="22.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2300,10 +2304,10 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
+        <v>41</v>
+      </c>
+      <c r="C98" t="s">
         <v>91</v>
-      </c>
-      <c r="C98" t="s">
-        <v>92</v>
       </c>
       <c r="D98" t="s">
         <v>8</v>
@@ -2317,10 +2321,10 @@
         <v>10</v>
       </c>
       <c r="B99" t="s">
+        <v>92</v>
+      </c>
+      <c r="C99" t="s">
         <v>91</v>
-      </c>
-      <c r="C99" t="s">
-        <v>92</v>
       </c>
       <c r="D99" t="s">
         <v>8</v>
@@ -2334,15 +2338,202 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
+        <v>49</v>
+      </c>
+      <c r="C100" t="s">
         <v>91</v>
       </c>
-      <c r="C100" t="s">
-        <v>92</v>
-      </c>
       <c r="D100" t="s">
         <v>8</v>
       </c>
       <c r="E100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>13</v>
+      </c>
+      <c r="B101" t="s">
+        <v>50</v>
+      </c>
+      <c r="C101" t="s">
+        <v>91</v>
+      </c>
+      <c r="D101" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" t="s">
+        <v>91</v>
+      </c>
+      <c r="D102" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B103" t="s">
+        <v>88</v>
+      </c>
+      <c r="C103" t="s">
+        <v>91</v>
+      </c>
+      <c r="D103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" t="s">
+        <v>89</v>
+      </c>
+      <c r="C104" t="s">
+        <v>91</v>
+      </c>
+      <c r="D104" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" t="s">
+        <v>91</v>
+      </c>
+      <c r="D105" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>13</v>
+      </c>
+      <c r="B106" t="s">
+        <v>49</v>
+      </c>
+      <c r="C106" t="s">
+        <v>93</v>
+      </c>
+      <c r="D106" t="s">
+        <v>8</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B107" t="s">
+        <v>50</v>
+      </c>
+      <c r="C107" t="s">
+        <v>93</v>
+      </c>
+      <c r="D107" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>13</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>93</v>
+      </c>
+      <c r="D108" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>13</v>
+      </c>
+      <c r="B109" t="s">
+        <v>28</v>
+      </c>
+      <c r="C109" t="s">
+        <v>93</v>
+      </c>
+      <c r="D109" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110" t="s">
+        <v>40</v>
+      </c>
+      <c r="C110" t="s">
+        <v>93</v>
+      </c>
+      <c r="D110" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>13</v>
+      </c>
+      <c r="B111" t="s">
+        <v>90</v>
+      </c>
+      <c r="C111" t="s">
+        <v>93</v>
+      </c>
+      <c r="D111" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111">
         <v>0</v>
       </c>
     </row>

--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="99">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -301,6 +301,21 @@
   </si>
   <si>
     <t>Null Check</t>
+  </si>
+  <si>
+    <t>ACR Calculation</t>
+  </si>
+  <si>
+    <t>Formula Validation</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>GCR Calculation</t>
+  </si>
+  <si>
+    <t>Gross AR Calculation</t>
   </si>
 </sst>
 </file>
@@ -640,14 +655,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" customWidth="1"/>
+    <col min="2" max="3" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2537,6 +2551,57 @@
         <v>0</v>
       </c>
     </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>13</v>
+      </c>
+      <c r="B112" t="s">
+        <v>94</v>
+      </c>
+      <c r="C112" t="s">
+        <v>95</v>
+      </c>
+      <c r="D112" t="s">
+        <v>96</v>
+      </c>
+      <c r="E112">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>13</v>
+      </c>
+      <c r="B113" t="s">
+        <v>97</v>
+      </c>
+      <c r="C113" t="s">
+        <v>95</v>
+      </c>
+      <c r="D113" t="s">
+        <v>96</v>
+      </c>
+      <c r="E113">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B114" t="s">
+        <v>98</v>
+      </c>
+      <c r="C114" t="s">
+        <v>95</v>
+      </c>
+      <c r="D114" t="s">
+        <v>96</v>
+      </c>
+      <c r="E114">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -309,13 +309,13 @@
     <t>Formula Validation</t>
   </si>
   <si>
+    <t>GCR Calculation</t>
+  </si>
+  <si>
+    <t>Gross AR Calculation</t>
+  </si>
+  <si>
     <t>F</t>
-  </si>
-  <si>
-    <t>GCR Calculation</t>
-  </si>
-  <si>
-    <t>Gross AR Calculation</t>
   </si>
 </sst>
 </file>
@@ -658,10 +658,11 @@
   <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" customWidth="1"/>
-    <col min="2" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2562,10 +2563,10 @@
         <v>95</v>
       </c>
       <c r="D112" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="E112">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -2573,16 +2574,16 @@
         <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C113" t="s">
         <v>95</v>
       </c>
       <c r="D113" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="E113">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -2590,13 +2591,13 @@
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C114" t="s">
         <v>95</v>
       </c>
       <c r="D114" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E114">
         <v>9</v>

--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="123">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -342,6 +342,9 @@
     <t>Latest Transaction Date should be less than Latest Loaded Date</t>
   </si>
   <si>
+    <t>Data Validation</t>
+  </si>
+  <si>
     <t>Business Rule Validation</t>
   </si>
   <si>
@@ -351,13 +354,19 @@
     <t>Practice Status of KPI sheet should match with Problem Reason of Practice Detail sheet</t>
   </si>
   <si>
-    <t>FIN Reconciliation</t>
+    <t>Current Charges</t>
   </si>
   <si>
     <t>Reconciliation Validation</t>
   </si>
   <si>
-    <t>Aging Reconciliation</t>
+    <t>Current Payments</t>
+  </si>
+  <si>
+    <t>Current Adjustments</t>
+  </si>
+  <si>
+    <t>Gross AR</t>
   </si>
   <si>
     <t>Practice Status Validation</t>
@@ -372,16 +381,13 @@
     <t>Practice Availability Validation</t>
   </si>
   <si>
-    <t>FIN Metrics</t>
-  </si>
-  <si>
     <t>Trend Validation</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>AR Metrics</t>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Current Encounters</t>
   </si>
 </sst>
 </file>
@@ -721,15 +727,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="53.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="29.44140625" customWidth="1"/>
+    <col min="2" max="2" width="80.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -3563,13 +3569,13 @@
         <v>107</v>
       </c>
       <c r="D142" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E142" t="s">
         <v>104</v>
       </c>
       <c r="F142">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -3577,13 +3583,13 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C143" t="s">
         <v>107</v>
       </c>
       <c r="D143" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -3597,13 +3603,13 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C144" t="s">
         <v>107</v>
       </c>
       <c r="D144" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E144" t="s">
         <v>104</v>
@@ -3617,19 +3623,19 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C145" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D145" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E145" t="s">
         <v>104</v>
       </c>
       <c r="F145">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -3637,76 +3643,76 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
+        <v>113</v>
+      </c>
+      <c r="C146" t="s">
+        <v>107</v>
+      </c>
+      <c r="D146" t="s">
         <v>112</v>
-      </c>
-      <c r="C146" t="s">
-        <v>111</v>
-      </c>
-      <c r="D146" t="s">
-        <v>111</v>
       </c>
       <c r="E146" t="s">
         <v>104</v>
       </c>
       <c r="F146">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C147" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D147" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E147" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>115</v>
+      </c>
+      <c r="C148" t="s">
+        <v>107</v>
+      </c>
+      <c r="D148" t="s">
+        <v>112</v>
+      </c>
+      <c r="E148" t="s">
+        <v>104</v>
+      </c>
+      <c r="F148">
         <v>12</v>
-      </c>
-      <c r="B148" t="s">
-        <v>116</v>
-      </c>
-      <c r="C148" t="s">
-        <v>114</v>
-      </c>
-      <c r="D148" t="s">
-        <v>114</v>
-      </c>
-      <c r="E148" t="s">
-        <v>115</v>
-      </c>
-      <c r="F148">
-        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B149" t="s">
+        <v>116</v>
+      </c>
+      <c r="C149" t="s">
+        <v>107</v>
+      </c>
+      <c r="D149" t="s">
         <v>117</v>
       </c>
-      <c r="C149" t="s">
+      <c r="E149" t="s">
         <v>118</v>
-      </c>
-      <c r="D149" t="s">
-        <v>118</v>
-      </c>
-      <c r="E149" t="s">
-        <v>119</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -3714,22 +3720,122 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
+        <v>119</v>
+      </c>
+      <c r="C150" t="s">
+        <v>107</v>
+      </c>
+      <c r="D150" t="s">
+        <v>117</v>
+      </c>
+      <c r="E150" t="s">
+        <v>118</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>111</v>
+      </c>
+      <c r="C151" t="s">
+        <v>107</v>
+      </c>
+      <c r="D151" t="s">
         <v>120</v>
       </c>
-      <c r="C150" t="s">
-        <v>118</v>
-      </c>
-      <c r="D150" t="s">
-        <v>118</v>
-      </c>
-      <c r="E150" t="s">
-        <v>119</v>
-      </c>
-      <c r="F150">
-        <v>0</v>
+      <c r="E151" t="s">
+        <v>121</v>
+      </c>
+      <c r="F151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>113</v>
+      </c>
+      <c r="C152" t="s">
+        <v>107</v>
+      </c>
+      <c r="D152" t="s">
+        <v>120</v>
+      </c>
+      <c r="E152" t="s">
+        <v>121</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>114</v>
+      </c>
+      <c r="C153" t="s">
+        <v>107</v>
+      </c>
+      <c r="D153" t="s">
+        <v>120</v>
+      </c>
+      <c r="E153" t="s">
+        <v>121</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>122</v>
+      </c>
+      <c r="C154" t="s">
+        <v>107</v>
+      </c>
+      <c r="D154" t="s">
+        <v>120</v>
+      </c>
+      <c r="E154" t="s">
+        <v>121</v>
+      </c>
+      <c r="F154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>115</v>
+      </c>
+      <c r="C155" t="s">
+        <v>107</v>
+      </c>
+      <c r="D155" t="s">
+        <v>120</v>
+      </c>
+      <c r="E155" t="s">
+        <v>121</v>
+      </c>
+      <c r="F155">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -339,16 +339,16 @@
     <t>Numeric Precision</t>
   </si>
   <si>
+    <t>Latest Transaction Date should be less than Latest Loaded Date</t>
+  </si>
+  <si>
+    <t>Data Validation</t>
+  </si>
+  <si>
+    <t>Business Rule Validation</t>
+  </si>
+  <si>
     <t>F</t>
-  </si>
-  <si>
-    <t>Latest Transaction Date should be less than Latest Loaded Date</t>
-  </si>
-  <si>
-    <t>Data Validation</t>
-  </si>
-  <si>
-    <t>Business Rule Validation</t>
   </si>
   <si>
     <t>Latest Transaction Date older than 3 months should display No LatestTransactionDate or NULL</t>
@@ -727,12 +727,12 @@
   <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.44140625" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -3449,10 +3449,10 @@
         <v>105</v>
       </c>
       <c r="E136" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="F136">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -3469,10 +3469,10 @@
         <v>105</v>
       </c>
       <c r="E137" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="F137">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -3489,10 +3489,10 @@
         <v>105</v>
       </c>
       <c r="E138" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="F138">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -3560,16 +3560,16 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
+        <v>106</v>
+      </c>
+      <c r="C142" t="s">
         <v>107</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>108</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>109</v>
-      </c>
-      <c r="E142" t="s">
-        <v>106</v>
       </c>
       <c r="F142">
         <v>13</v>
@@ -3583,10 +3583,10 @@
         <v>110</v>
       </c>
       <c r="C143" t="s">
+        <v>107</v>
+      </c>
+      <c r="D143" t="s">
         <v>108</v>
-      </c>
-      <c r="D143" t="s">
-        <v>109</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -3603,13 +3603,13 @@
         <v>111</v>
       </c>
       <c r="C144" t="s">
+        <v>107</v>
+      </c>
+      <c r="D144" t="s">
         <v>108</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>109</v>
-      </c>
-      <c r="E144" t="s">
-        <v>106</v>
       </c>
       <c r="F144">
         <v>2</v>
@@ -3623,13 +3623,13 @@
         <v>112</v>
       </c>
       <c r="C145" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D145" t="s">
         <v>113</v>
       </c>
       <c r="E145" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F145">
         <v>3</v>
@@ -3643,13 +3643,13 @@
         <v>114</v>
       </c>
       <c r="C146" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D146" t="s">
         <v>113</v>
       </c>
       <c r="E146" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F146">
         <v>2</v>
@@ -3663,13 +3663,13 @@
         <v>115</v>
       </c>
       <c r="C147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D147" t="s">
         <v>113</v>
       </c>
       <c r="E147" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F147">
         <v>3</v>
@@ -3683,13 +3683,13 @@
         <v>116</v>
       </c>
       <c r="C148" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D148" t="s">
         <v>113</v>
       </c>
       <c r="E148" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F148">
         <v>5</v>
@@ -3703,7 +3703,7 @@
         <v>117</v>
       </c>
       <c r="C149" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D149" t="s">
         <v>118</v>
@@ -3723,7 +3723,7 @@
         <v>119</v>
       </c>
       <c r="C150" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D150" t="s">
         <v>118</v>
@@ -3743,16 +3743,16 @@
         <v>112</v>
       </c>
       <c r="C151" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D151" t="s">
         <v>120</v>
       </c>
       <c r="E151" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -3763,16 +3763,16 @@
         <v>114</v>
       </c>
       <c r="C152" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D152" t="s">
         <v>120</v>
       </c>
       <c r="E152" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F152">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -3783,16 +3783,16 @@
         <v>115</v>
       </c>
       <c r="C153" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D153" t="s">
         <v>120</v>
       </c>
       <c r="E153" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F153">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -3803,16 +3803,16 @@
         <v>121</v>
       </c>
       <c r="C154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D154" t="s">
         <v>120</v>
       </c>
       <c r="E154" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
@@ -3823,7 +3823,7 @@
         <v>116</v>
       </c>
       <c r="C155" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D155" t="s">
         <v>120</v>

--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -727,12 +727,12 @@
   <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -3752,7 +3752,7 @@
         <v>109</v>
       </c>
       <c r="F151">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -3772,7 +3772,7 @@
         <v>109</v>
       </c>
       <c r="F152">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -3792,7 +3792,7 @@
         <v>109</v>
       </c>
       <c r="F153">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -3812,7 +3812,7 @@
         <v>109</v>
       </c>
       <c r="F154">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">

--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$155</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -727,12 +730,12 @@
   <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="54.88671875" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -3829,13 +3832,14 @@
         <v>120</v>
       </c>
       <c r="E155" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="121">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -342,6 +342,9 @@
     <t>Numeric Precision</t>
   </si>
   <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>Latest Transaction Date should be less than Latest Loaded Date</t>
   </si>
   <si>
@@ -351,13 +354,7 @@
     <t>Business Rule Validation</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>Latest Transaction Date older than 3 months should display No LatestTransactionDate or NULL</t>
-  </si>
-  <si>
-    <t>Practice Status of KPI sheet should match with Problem Reason of Practice Detail sheet</t>
   </si>
   <si>
     <t>Current Charges</t>
@@ -730,12 +727,12 @@
   <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -3452,10 +3449,10 @@
         <v>105</v>
       </c>
       <c r="E136" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -3472,10 +3469,10 @@
         <v>105</v>
       </c>
       <c r="E137" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -3492,10 +3489,10 @@
         <v>105</v>
       </c>
       <c r="E138" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -3563,16 +3560,16 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
+        <v>107</v>
+      </c>
+      <c r="C142" t="s">
+        <v>108</v>
+      </c>
+      <c r="D142" t="s">
+        <v>109</v>
+      </c>
+      <c r="E142" t="s">
         <v>106</v>
-      </c>
-      <c r="C142" t="s">
-        <v>107</v>
-      </c>
-      <c r="D142" t="s">
-        <v>108</v>
-      </c>
-      <c r="E142" t="s">
-        <v>109</v>
       </c>
       <c r="F142">
         <v>13</v>
@@ -3586,10 +3583,10 @@
         <v>110</v>
       </c>
       <c r="C143" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D143" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -3603,19 +3600,19 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="C144" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D144" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E144" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F144">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -3623,16 +3620,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
+        <v>111</v>
+      </c>
+      <c r="C145" t="s">
+        <v>108</v>
+      </c>
+      <c r="D145" t="s">
         <v>112</v>
       </c>
-      <c r="C145" t="s">
-        <v>107</v>
-      </c>
-      <c r="D145" t="s">
-        <v>113</v>
-      </c>
       <c r="E145" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F145">
         <v>3</v>
@@ -3643,16 +3640,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C146" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D146" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E146" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F146">
         <v>2</v>
@@ -3663,16 +3660,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C147" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D147" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E147" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F147">
         <v>3</v>
@@ -3683,16 +3680,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C148" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D148" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E148" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F148">
         <v>5</v>
@@ -3703,19 +3700,19 @@
         <v>13</v>
       </c>
       <c r="B149" t="s">
+        <v>116</v>
+      </c>
+      <c r="C149" t="s">
+        <v>108</v>
+      </c>
+      <c r="D149" t="s">
         <v>117</v>
       </c>
-      <c r="C149" t="s">
-        <v>107</v>
-      </c>
-      <c r="D149" t="s">
-        <v>118</v>
-      </c>
       <c r="E149" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -3723,19 +3720,19 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C150" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D150" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E150" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
@@ -3743,16 +3740,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C151" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D151" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E151" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F151">
         <v>18</v>
@@ -3763,16 +3760,16 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C152" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D152" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E152" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F152">
         <v>19</v>
@@ -3783,16 +3780,16 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C153" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D153" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E153" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F153">
         <v>22</v>
@@ -3803,16 +3800,16 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C154" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D154" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E154" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F154">
         <v>12</v>
@@ -3823,16 +3820,16 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C155" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D155" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E155" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F155">
         <v>4</v>

--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnisLink Intern\KPI_Automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnisLink Intern\KPI_Automation_Framework\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,9 +14,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$155</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -727,12 +724,11 @@
   <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.109375" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -3836,7 +3832,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnisLink Intern\KPI_Automation_Framework\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnisLink Intern\KPI_Automation_Framework\KPI_Automation_Framework\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$146</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="116">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -57,6 +60,9 @@
     <t>Data Pipeline Status</t>
   </si>
   <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>Data Currency</t>
   </si>
   <si>
@@ -69,126 +75,108 @@
     <t>KPI</t>
   </si>
   <si>
+    <t>Field Validation</t>
+  </si>
+  <si>
+    <t>Field Existence Testing</t>
+  </si>
+  <si>
+    <t>Groups</t>
+  </si>
+  <si>
     <t>Platform</t>
   </si>
   <si>
-    <t>Field Validation</t>
-  </si>
-  <si>
-    <t>Field Existence Testing</t>
+    <t>AccountStatus</t>
+  </si>
+  <si>
+    <t>ClientRisk</t>
+  </si>
+  <si>
+    <t>DBPracticename</t>
+  </si>
+  <si>
+    <t>PracticeCode</t>
+  </si>
+  <si>
+    <t>LatestTransactionDate</t>
+  </si>
+  <si>
+    <t>LastLoadedDate</t>
+  </si>
+  <si>
+    <t>FinReconcilationstatus</t>
+  </si>
+  <si>
+    <t>AgingReconcilationstatus</t>
+  </si>
+  <si>
+    <t>FinalReconcilationstatus</t>
+  </si>
+  <si>
+    <t>DataRefreshStatus</t>
+  </si>
+  <si>
+    <t>DataRefreshFrequency</t>
+  </si>
+  <si>
+    <t>IsFinAvailable</t>
+  </si>
+  <si>
+    <t>IsAgingavailable</t>
+  </si>
+  <si>
+    <t>isavailable</t>
+  </si>
+  <si>
+    <t>platform</t>
+  </si>
+  <si>
+    <t>DBPracticeName</t>
+  </si>
+  <si>
+    <t>practicecode</t>
+  </si>
+  <si>
+    <t>EnterpriseClientName</t>
+  </si>
+  <si>
+    <t>NetSuiteNumber</t>
+  </si>
+  <si>
+    <t>GoLiveDate</t>
+  </si>
+  <si>
+    <t>OnboardingDate</t>
+  </si>
+  <si>
+    <t>WinddownStartDate</t>
+  </si>
+  <si>
+    <t>AutomaticExtractionMethod</t>
+  </si>
+  <si>
+    <t>ProblemReason</t>
+  </si>
+  <si>
+    <t>FiscalYear</t>
+  </si>
+  <si>
+    <t>FiscalMonth</t>
+  </si>
+  <si>
+    <t>Speciality</t>
+  </si>
+  <si>
+    <t>Service Provider</t>
+  </si>
+  <si>
+    <t>Billing Provider</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Billing Provider</t>
-  </si>
-  <si>
-    <t>Service Provider</t>
-  </si>
-  <si>
-    <t>DxCode</t>
-  </si>
-  <si>
-    <t>POS</t>
-  </si>
-  <si>
-    <t>Modifier</t>
-  </si>
-  <si>
-    <t>Provider ID</t>
-  </si>
-  <si>
-    <t>Referring Provider</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Groups</t>
-  </si>
-  <si>
-    <t>AccountStatus</t>
-  </si>
-  <si>
-    <t>ClientRisk</t>
-  </si>
-  <si>
-    <t>DBPracticename</t>
-  </si>
-  <si>
-    <t>PracticeCode</t>
-  </si>
-  <si>
-    <t>LatestTransactionDate</t>
-  </si>
-  <si>
-    <t>LastLoadedDate</t>
-  </si>
-  <si>
-    <t>FinReconcilationstatus</t>
-  </si>
-  <si>
-    <t>AgingReconcilationstatus</t>
-  </si>
-  <si>
-    <t>FinalReconcilationstatus</t>
-  </si>
-  <si>
-    <t>DataRefreshStatus</t>
-  </si>
-  <si>
-    <t>DataRefreshFrequency</t>
-  </si>
-  <si>
-    <t>IsFinAvailable</t>
-  </si>
-  <si>
-    <t>IsAgingavailable</t>
-  </si>
-  <si>
-    <t>isavailable</t>
-  </si>
-  <si>
-    <t>platform</t>
-  </si>
-  <si>
-    <t>DBPracticeName</t>
-  </si>
-  <si>
-    <t>practicecode</t>
-  </si>
-  <si>
-    <t>EnterpriseClientName</t>
-  </si>
-  <si>
-    <t>NetSuiteNumber</t>
-  </si>
-  <si>
-    <t>GoLiveDate</t>
-  </si>
-  <si>
-    <t>OnboardingDate</t>
-  </si>
-  <si>
-    <t>WinddownStartDate</t>
-  </si>
-  <si>
-    <t>AutomaticExtractionMethod</t>
-  </si>
-  <si>
-    <t>ProblemReason</t>
-  </si>
-  <si>
-    <t>FiscalYear</t>
-  </si>
-  <si>
-    <t>FiscalMonth</t>
-  </si>
-  <si>
-    <t>Speciality</t>
-  </si>
-  <si>
     <t>Current_Charges</t>
   </si>
   <si>
@@ -339,9 +327,6 @@
     <t>Numeric Precision</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>Latest Transaction Date should be less than Latest Loaded Date</t>
   </si>
   <si>
@@ -352,6 +337,9 @@
   </si>
   <si>
     <t>Latest Transaction Date older than 3 months should display No LatestTransactionDate or NULL</t>
+  </si>
+  <si>
+    <t>Practice Status of KPI sheet should match with Problem Reason of Practice Detail sheet</t>
   </si>
   <si>
     <t>Current Charges</t>
@@ -721,14 +709,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
-    <col min="3" max="3" width="24.109375" customWidth="1"/>
-    <col min="4" max="4" width="20.77734375" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -785,15 +774,15 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -813,7 +802,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -833,7 +822,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -853,7 +842,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -876,7 +865,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -885,15 +874,15 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -913,7 +902,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
@@ -925,15 +914,15 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -953,7 +942,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
@@ -973,7 +962,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
@@ -993,7 +982,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1013,7 +1002,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
@@ -1033,7 +1022,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -1053,7 +1042,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
@@ -1073,7 +1062,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
@@ -1093,10 +1082,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>17</v>
@@ -1113,10 +1102,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
         <v>17</v>
@@ -1133,10 +1122,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
@@ -1153,10 +1142,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -1173,10 +1162,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -1193,10 +1182,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -1213,10 +1202,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -1233,7 +1222,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -1253,7 +1242,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -1273,7 +1262,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1293,10 +1282,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -1313,10 +1302,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -1333,10 +1322,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
         <v>17</v>
@@ -1353,10 +1342,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
@@ -1373,10 +1362,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
         <v>17</v>
@@ -1393,10 +1382,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
@@ -1413,10 +1402,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
@@ -1433,10 +1422,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
         <v>17</v>
@@ -1453,10 +1442,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
@@ -1473,10 +1462,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
@@ -1493,10 +1482,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
@@ -1513,10 +1502,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
@@ -1533,10 +1522,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
@@ -1553,10 +1542,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
@@ -1573,10 +1562,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
@@ -1593,10 +1582,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
         <v>17</v>
@@ -1613,10 +1602,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
@@ -1633,10 +1622,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
@@ -1653,10 +1642,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
@@ -1673,10 +1662,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
@@ -1693,10 +1682,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
@@ -1713,10 +1702,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
@@ -1733,10 +1722,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
@@ -1753,10 +1742,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
@@ -1773,10 +1762,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
@@ -1793,10 +1782,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
@@ -1813,10 +1802,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
@@ -1833,10 +1822,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
@@ -1853,10 +1842,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
@@ -1873,10 +1862,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
@@ -1893,10 +1882,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
@@ -1913,10 +1902,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
@@ -1933,10 +1922,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
@@ -1953,10 +1942,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
@@ -1973,10 +1962,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
@@ -1993,10 +1982,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
@@ -2013,10 +2002,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
@@ -2033,10 +2022,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
@@ -2053,10 +2042,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
@@ -2073,10 +2062,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
@@ -2093,10 +2082,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C69" t="s">
         <v>17</v>
@@ -2113,10 +2102,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
@@ -2133,10 +2122,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B71" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
@@ -2153,10 +2142,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B72" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
@@ -2173,10 +2162,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
@@ -2193,10 +2182,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
@@ -2213,10 +2202,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
@@ -2233,10 +2222,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
@@ -2253,10 +2242,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
@@ -2273,10 +2262,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
@@ -2293,10 +2282,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
@@ -2313,10 +2302,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
@@ -2333,10 +2322,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
@@ -2353,10 +2342,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
@@ -2373,10 +2362,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
         <v>17</v>
@@ -2393,10 +2382,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B84" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
         <v>17</v>
@@ -2413,10 +2402,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
@@ -2433,10 +2422,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
         <v>17</v>
@@ -2453,10 +2442,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
@@ -2473,10 +2462,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B88" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
@@ -2493,16 +2482,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D89" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -2513,16 +2502,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -2533,116 +2522,116 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C91" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="E91" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D95" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="C96" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D96" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -2653,16 +2642,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
@@ -2673,16 +2662,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C98" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D98" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
@@ -2693,16 +2682,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="C99" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D99" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
@@ -2713,16 +2702,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D100" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -2733,13 +2722,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="C101" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D101" t="s">
         <v>100</v>
@@ -2753,16 +2742,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="C102" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D102" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -2773,16 +2762,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="C103" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D103" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -2793,16 +2782,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="C104" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D104" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
@@ -2813,16 +2802,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B105" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C105" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D105" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -2833,16 +2822,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B106" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C106" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D106" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -2853,16 +2842,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C107" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D107" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -2873,16 +2862,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B108" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C108" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D108" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
@@ -2893,16 +2882,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B109" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C109" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D109" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
@@ -2913,16 +2902,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B110" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C110" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D110" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
@@ -2933,16 +2922,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B111" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C111" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D111" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
@@ -2953,16 +2942,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B112" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C112" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D112" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
@@ -2973,16 +2962,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B113" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C113" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D113" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
@@ -2993,16 +2982,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B114" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C114" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D114" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -3013,16 +3002,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B115" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C115" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D115" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
@@ -3033,16 +3022,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B116" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C116" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D116" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -3053,16 +3042,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B117" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C117" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D117" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
@@ -3073,16 +3062,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C118" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D118" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
@@ -3093,16 +3082,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B119" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C119" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D119" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
@@ -3113,16 +3102,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B120" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C120" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D120" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E120" t="s">
         <v>10</v>
@@ -3133,16 +3122,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C121" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D121" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E121" t="s">
         <v>10</v>
@@ -3153,16 +3142,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C122" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D122" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E122" t="s">
         <v>10</v>
@@ -3173,16 +3162,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C123" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D123" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E123" t="s">
         <v>10</v>
@@ -3193,16 +3182,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B124" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C124" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D124" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E124" t="s">
         <v>10</v>
@@ -3213,16 +3202,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B125" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C125" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D125" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E125" t="s">
         <v>10</v>
@@ -3233,16 +3222,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B126" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C126" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D126" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E126" t="s">
         <v>10</v>
@@ -3253,36 +3242,36 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B127" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C127" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D127" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E127" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B128" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C128" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D128" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
@@ -3293,16 +3282,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B129" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C129" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D129" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E129" t="s">
         <v>10</v>
@@ -3313,16 +3302,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B130" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C130" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D130" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
@@ -3333,16 +3322,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B131" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C131" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D131" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
@@ -3353,16 +3342,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B132" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C132" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D132" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
@@ -3373,465 +3362,286 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C133" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D133" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E133" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B134" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C134" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D134" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E134" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B135" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C135" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D135" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E135" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B136" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C136" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D136" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E136" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="F136">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B137" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C137" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D137" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E137" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="F137">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B138" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C138" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D138" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E138" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="F138">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B139" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C139" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D139" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E139" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B140" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C140" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D140" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E140" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B141" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C141" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D141" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E141" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>16</v>
+      </c>
+      <c r="B142" t="s">
+        <v>106</v>
+      </c>
+      <c r="C142" t="s">
+        <v>102</v>
+      </c>
+      <c r="D142" t="s">
+        <v>114</v>
+      </c>
+      <c r="E142" t="s">
         <v>12</v>
       </c>
-      <c r="B142" t="s">
-        <v>107</v>
-      </c>
-      <c r="C142" t="s">
-        <v>108</v>
-      </c>
-      <c r="D142" t="s">
-        <v>109</v>
-      </c>
-      <c r="E142" t="s">
-        <v>106</v>
-      </c>
       <c r="F142">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>16</v>
+      </c>
+      <c r="B143" t="s">
+        <v>108</v>
+      </c>
+      <c r="C143" t="s">
+        <v>102</v>
+      </c>
+      <c r="D143" t="s">
+        <v>114</v>
+      </c>
+      <c r="E143" t="s">
         <v>12</v>
       </c>
-      <c r="B143" t="s">
-        <v>110</v>
-      </c>
-      <c r="C143" t="s">
-        <v>108</v>
-      </c>
-      <c r="D143" t="s">
-        <v>109</v>
-      </c>
-      <c r="E143" t="s">
-        <v>10</v>
-      </c>
       <c r="F143">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B144" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="C144" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D144" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E144" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="F144">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B145" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C145" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D145" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E145" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="F145">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B146" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C146" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D146" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E146" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="F146">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>114</v>
-      </c>
-      <c r="C147" t="s">
-        <v>108</v>
-      </c>
-      <c r="D147" t="s">
-        <v>112</v>
-      </c>
-      <c r="E147" t="s">
-        <v>106</v>
-      </c>
-      <c r="F147">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>115</v>
-      </c>
-      <c r="C148" t="s">
-        <v>108</v>
-      </c>
-      <c r="D148" t="s">
-        <v>112</v>
-      </c>
-      <c r="E148" t="s">
-        <v>106</v>
-      </c>
-      <c r="F148">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>13</v>
-      </c>
-      <c r="B149" t="s">
-        <v>116</v>
-      </c>
-      <c r="C149" t="s">
-        <v>108</v>
-      </c>
-      <c r="D149" t="s">
-        <v>117</v>
-      </c>
-      <c r="E149" t="s">
-        <v>106</v>
-      </c>
-      <c r="F149">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>12</v>
-      </c>
-      <c r="B150" t="s">
-        <v>118</v>
-      </c>
-      <c r="C150" t="s">
-        <v>108</v>
-      </c>
-      <c r="D150" t="s">
-        <v>117</v>
-      </c>
-      <c r="E150" t="s">
-        <v>106</v>
-      </c>
-      <c r="F150">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>111</v>
-      </c>
-      <c r="C151" t="s">
-        <v>108</v>
-      </c>
-      <c r="D151" t="s">
-        <v>119</v>
-      </c>
-      <c r="E151" t="s">
-        <v>106</v>
-      </c>
-      <c r="F151">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>113</v>
-      </c>
-      <c r="C152" t="s">
-        <v>108</v>
-      </c>
-      <c r="D152" t="s">
-        <v>119</v>
-      </c>
-      <c r="E152" t="s">
-        <v>106</v>
-      </c>
-      <c r="F152">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>114</v>
-      </c>
-      <c r="C153" t="s">
-        <v>108</v>
-      </c>
-      <c r="D153" t="s">
-        <v>119</v>
-      </c>
-      <c r="E153" t="s">
-        <v>106</v>
-      </c>
-      <c r="F153">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>120</v>
-      </c>
-      <c r="C154" t="s">
-        <v>108</v>
-      </c>
-      <c r="D154" t="s">
-        <v>119</v>
-      </c>
-      <c r="E154" t="s">
-        <v>106</v>
-      </c>
-      <c r="F154">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>115</v>
-      </c>
-      <c r="C155" t="s">
-        <v>108</v>
-      </c>
-      <c r="D155" t="s">
-        <v>119</v>
-      </c>
-      <c r="E155" t="s">
-        <v>106</v>
-      </c>
-      <c r="F155">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>